--- a/Team-Data/2013-14/2-4-2013-14.xlsx
+++ b/Team-Data/2013-14/2-4-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,61 +728,61 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E2" t="n">
         <v>25</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" t="n">
-        <v>0.532</v>
+        <v>0.543</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
       </c>
       <c r="I2" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="J2" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>0.462</v>
       </c>
       <c r="L2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>25</v>
       </c>
       <c r="N2" t="n">
-        <v>0.37</v>
+        <v>0.372</v>
       </c>
       <c r="O2" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P2" t="n">
-        <v>21.7</v>
+        <v>21.9</v>
       </c>
       <c r="Q2" t="n">
         <v>0.785</v>
       </c>
       <c r="R2" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S2" t="n">
         <v>31.7</v>
       </c>
       <c r="T2" t="n">
-        <v>40.9</v>
+        <v>41</v>
       </c>
       <c r="U2" t="n">
         <v>25.7</v>
       </c>
       <c r="V2" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W2" t="n">
         <v>9</v>
@@ -724,40 +791,40 @@
         <v>4.4</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Z2" t="n">
         <v>19</v>
       </c>
       <c r="AA2" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB2" t="n">
-        <v>102.7</v>
+        <v>103.1</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE2" t="n">
         <v>13</v>
       </c>
       <c r="AF2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG2" t="n">
         <v>12</v>
       </c>
-      <c r="AG2" t="n">
-        <v>13</v>
-      </c>
       <c r="AH2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AK2" t="n">
         <v>7</v>
@@ -769,16 +836,16 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO2" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP2" t="n">
         <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR2" t="n">
         <v>25</v>
@@ -796,13 +863,13 @@
         <v>22</v>
       </c>
       <c r="AW2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AX2" t="n">
         <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AZ2" t="n">
         <v>5</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>23</v>
@@ -939,7 +1006,7 @@
         <v>25</v>
       </c>
       <c r="AJ3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK3" t="n">
         <v>26</v>
@@ -954,7 +1021,7 @@
         <v>28</v>
       </c>
       <c r="AO3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -1103,10 +1170,10 @@
         <v>-2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF4" t="n">
         <v>18</v>
@@ -1133,7 +1200,7 @@
         <v>13</v>
       </c>
       <c r="AN4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
         <v>6</v>
@@ -1178,7 +1245,7 @@
         <v>21</v>
       </c>
       <c r="BC4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" t="n">
         <v>28</v>
       </c>
       <c r="G5" t="n">
-        <v>0.44</v>
+        <v>0.429</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1225,37 +1292,37 @@
         <v>35.3</v>
       </c>
       <c r="J5" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K5" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
       <c r="L5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>0.348</v>
+        <v>0.347</v>
       </c>
       <c r="O5" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P5" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.728</v>
+        <v>0.729</v>
       </c>
       <c r="R5" t="n">
         <v>9</v>
       </c>
       <c r="S5" t="n">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="T5" t="n">
-        <v>42</v>
+        <v>41.9</v>
       </c>
       <c r="U5" t="n">
         <v>20.4</v>
@@ -1264,10 +1331,10 @@
         <v>12.8</v>
       </c>
       <c r="W5" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="n">
         <v>5.5</v>
@@ -1276,16 +1343,16 @@
         <v>18.4</v>
       </c>
       <c r="AA5" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>94.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.6</v>
+        <v>-3</v>
       </c>
       <c r="AD5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
         <v>18</v>
@@ -1318,13 +1385,13 @@
         <v>22</v>
       </c>
       <c r="AO5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP5" t="n">
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AR5" t="n">
         <v>28</v>
@@ -1354,13 +1421,13 @@
         <v>3</v>
       </c>
       <c r="BA5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -1389,25 +1456,25 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F6" t="n">
         <v>24</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="H6" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I6" t="n">
         <v>34.1</v>
       </c>
       <c r="J6" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K6" t="n">
         <v>0.422</v>
@@ -1422,16 +1489,16 @@
         <v>0.335</v>
       </c>
       <c r="O6" t="n">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="P6" t="n">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.765</v>
+        <v>0.764</v>
       </c>
       <c r="R6" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S6" t="n">
         <v>32.5</v>
@@ -1440,43 +1507,43 @@
         <v>44.6</v>
       </c>
       <c r="U6" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="V6" t="n">
         <v>15.6</v>
       </c>
       <c r="W6" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y6" t="n">
         <v>6.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA6" t="n">
         <v>21.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.2</v>
+        <v>92</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF6" t="n">
         <v>16</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH6" t="n">
         <v>1</v>
@@ -1485,10 +1552,10 @@
         <v>30</v>
       </c>
       <c r="AJ6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL6" t="n">
         <v>28</v>
@@ -1503,19 +1570,19 @@
         <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ6" t="n">
         <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS6" t="n">
         <v>13</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU6" t="n">
         <v>13</v>
@@ -1524,7 +1591,7 @@
         <v>25</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
         <v>8</v>
@@ -1536,10 +1603,10 @@
         <v>6</v>
       </c>
       <c r="BA6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB6" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC6" t="n">
         <v>17</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -1649,19 +1716,19 @@
         <v>-6.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE7" t="n">
         <v>23</v>
       </c>
       <c r="AF7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI7" t="n">
         <v>22</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>1.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>10</v>
@@ -1864,7 +1931,7 @@
         <v>6</v>
       </c>
       <c r="AO8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP8" t="n">
         <v>24</v>
@@ -1888,7 +1955,7 @@
         <v>5</v>
       </c>
       <c r="AW8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX8" t="n">
         <v>25</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -2013,10 +2080,10 @@
         <v>0.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AF9" t="n">
         <v>14</v>
@@ -2031,7 +2098,7 @@
         <v>11</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK9" t="n">
         <v>14</v>
@@ -2052,10 +2119,10 @@
         <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AR9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS9" t="n">
         <v>5</v>
@@ -2067,10 +2134,10 @@
         <v>11</v>
       </c>
       <c r="AV9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX9" t="n">
         <v>4</v>
@@ -2082,7 +2149,7 @@
         <v>29</v>
       </c>
       <c r="BA9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB9" t="n">
         <v>9</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2210,7 +2277,7 @@
         <v>15</v>
       </c>
       <c r="AI10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
@@ -2228,7 +2295,7 @@
         <v>30</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP10" t="n">
         <v>4</v>
@@ -2258,7 +2325,7 @@
         <v>9</v>
       </c>
       <c r="AY10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ10" t="n">
         <v>14</v>
@@ -2270,7 +2337,7 @@
         <v>16</v>
       </c>
       <c r="BC10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -2299,58 +2366,58 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E11" t="n">
         <v>29</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G11" t="n">
-        <v>0.592</v>
+        <v>0.604</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>38.8</v>
+        <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>85</v>
+        <v>84.8</v>
       </c>
       <c r="K11" t="n">
-        <v>0.457</v>
+        <v>0.46</v>
       </c>
       <c r="L11" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="M11" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.38</v>
+        <v>0.383</v>
       </c>
       <c r="O11" t="n">
         <v>16.1</v>
       </c>
       <c r="P11" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.738</v>
+        <v>0.736</v>
       </c>
       <c r="R11" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S11" t="n">
-        <v>34.9</v>
+        <v>35</v>
       </c>
       <c r="T11" t="n">
-        <v>46.1</v>
+        <v>46</v>
       </c>
       <c r="U11" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V11" t="n">
         <v>16.3</v>
@@ -2365,19 +2432,19 @@
         <v>4.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA11" t="n">
         <v>19.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>103</v>
+        <v>103.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,28 +2456,28 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI11" t="n">
         <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2419,7 +2486,7 @@
         <v>23</v>
       </c>
       <c r="AR11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2440,7 +2507,7 @@
         <v>10</v>
       </c>
       <c r="AY11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
         <v>24</v>
@@ -2452,7 +2519,7 @@
         <v>11</v>
       </c>
       <c r="BC11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>3.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
@@ -2571,7 +2638,7 @@
         <v>7</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI12" t="n">
         <v>18</v>
@@ -2601,7 +2668,7 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
@@ -2634,7 +2701,7 @@
         <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E13" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F13" t="n">
         <v>10</v>
       </c>
       <c r="G13" t="n">
-        <v>0.792</v>
+        <v>0.787</v>
       </c>
       <c r="H13" t="n">
         <v>48.2</v>
@@ -2681,7 +2748,7 @@
         <v>36.7</v>
       </c>
       <c r="J13" t="n">
-        <v>80.8</v>
+        <v>81</v>
       </c>
       <c r="K13" t="n">
         <v>0.454</v>
@@ -2693,37 +2760,37 @@
         <v>19.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O13" t="n">
         <v>18.2</v>
       </c>
       <c r="P13" t="n">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="Q13" t="n">
         <v>0.78</v>
       </c>
       <c r="R13" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S13" t="n">
         <v>35.2</v>
       </c>
       <c r="T13" t="n">
-        <v>45.5</v>
+        <v>45.6</v>
       </c>
       <c r="U13" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V13" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W13" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Y13" t="n">
         <v>4.5</v>
@@ -2732,16 +2799,16 @@
         <v>20.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>98.40000000000001</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD13" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
@@ -2759,7 +2826,7 @@
         <v>20</v>
       </c>
       <c r="AJ13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK13" t="n">
         <v>12</v>
@@ -2771,10 +2838,10 @@
         <v>23</v>
       </c>
       <c r="AN13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AP13" t="n">
         <v>15</v>
@@ -2795,7 +2862,7 @@
         <v>20</v>
       </c>
       <c r="AV13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW13" t="n">
         <v>24</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -2953,7 +3020,7 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO14" t="n">
         <v>2</v>
@@ -2962,7 +3029,7 @@
         <v>2</v>
       </c>
       <c r="AQ14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR14" t="n">
         <v>22</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E15" t="n">
         <v>16</v>
       </c>
       <c r="F15" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G15" t="n">
-        <v>0.333</v>
+        <v>0.34</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
@@ -3045,7 +3112,7 @@
         <v>37</v>
       </c>
       <c r="J15" t="n">
-        <v>84.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K15" t="n">
         <v>0.44</v>
@@ -3054,37 +3121,37 @@
         <v>9.1</v>
       </c>
       <c r="M15" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="N15" t="n">
-        <v>0.369</v>
+        <v>0.367</v>
       </c>
       <c r="O15" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="P15" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.76</v>
+        <v>0.757</v>
       </c>
       <c r="R15" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T15" t="n">
-        <v>42.5</v>
+        <v>42.6</v>
       </c>
       <c r="U15" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V15" t="n">
         <v>15.1</v>
       </c>
       <c r="W15" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="X15" t="n">
         <v>5.5</v>
@@ -3093,19 +3160,19 @@
         <v>4.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA15" t="n">
         <v>19.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5.7</v>
+        <v>-5.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE15" t="n">
         <v>23</v>
@@ -3126,7 +3193,7 @@
         <v>10</v>
       </c>
       <c r="AK15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL15" t="n">
         <v>5</v>
@@ -3138,19 +3205,19 @@
         <v>12</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP15" t="n">
         <v>16</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR15" t="n">
         <v>24</v>
       </c>
       <c r="AS15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AT15" t="n">
         <v>20</v>
@@ -3159,7 +3226,7 @@
         <v>10</v>
       </c>
       <c r="AV15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
         <v>28</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -3469,7 +3536,7 @@
         <v>5.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3481,7 +3548,7 @@
         <v>4</v>
       </c>
       <c r="AH17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI17" t="n">
         <v>4</v>
@@ -3499,16 +3566,16 @@
         <v>15</v>
       </c>
       <c r="AN17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO17" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP17" t="n">
         <v>12</v>
       </c>
       <c r="AQ17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
@@ -3523,7 +3590,7 @@
         <v>7</v>
       </c>
       <c r="AV17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-9.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3672,7 +3739,7 @@
         <v>16</v>
       </c>
       <c r="AK18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL18" t="n">
         <v>17</v>
@@ -3723,7 +3790,7 @@
         <v>18</v>
       </c>
       <c r="BB18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BC18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F19" t="n">
         <v>24</v>
       </c>
       <c r="G19" t="n">
-        <v>0.5</v>
+        <v>0.489</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,7 +3840,7 @@
         <v>38.6</v>
       </c>
       <c r="J19" t="n">
-        <v>88.3</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K19" t="n">
         <v>0.437</v>
@@ -3782,31 +3849,31 @@
         <v>7.6</v>
       </c>
       <c r="M19" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.347</v>
+        <v>0.345</v>
       </c>
       <c r="O19" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="P19" t="n">
-        <v>27</v>
+        <v>26.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.784</v>
+        <v>0.786</v>
       </c>
       <c r="R19" t="n">
         <v>13</v>
       </c>
       <c r="S19" t="n">
-        <v>33</v>
+        <v>32.8</v>
       </c>
       <c r="T19" t="n">
-        <v>46</v>
+        <v>45.8</v>
       </c>
       <c r="U19" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V19" t="n">
         <v>13.8</v>
@@ -3815,7 +3882,7 @@
         <v>8.9</v>
       </c>
       <c r="X19" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Y19" t="n">
         <v>5.7</v>
@@ -3827,28 +3894,28 @@
         <v>22.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>106</v>
+        <v>105.9</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF19" t="n">
         <v>16</v>
       </c>
       <c r="AG19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AH19" t="n">
         <v>21</v>
       </c>
       <c r="AI19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ19" t="n">
         <v>1</v>
@@ -3863,7 +3930,7 @@
         <v>12</v>
       </c>
       <c r="AN19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO19" t="n">
         <v>3</v>
@@ -3872,13 +3939,13 @@
         <v>3</v>
       </c>
       <c r="AQ19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR19" t="n">
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AT19" t="n">
         <v>3</v>
@@ -3908,7 +3975,7 @@
         <v>3</v>
       </c>
       <c r="BC19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
@@ -4227,7 +4294,7 @@
         <v>7</v>
       </c>
       <c r="AN21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4488,7 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -4600,13 +4667,13 @@
         <v>23</v>
       </c>
       <c r="AQ23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR23" t="n">
         <v>26</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT23" t="n">
         <v>22</v>
@@ -4615,7 +4682,7 @@
         <v>21</v>
       </c>
       <c r="AV23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW23" t="n">
         <v>15</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE24" t="n">
         <v>28</v>
@@ -4764,7 +4831,7 @@
         <v>2</v>
       </c>
       <c r="AK24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL24" t="n">
         <v>22</v>
@@ -4779,7 +4846,7 @@
         <v>20</v>
       </c>
       <c r="AP24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4791,7 +4858,7 @@
         <v>12</v>
       </c>
       <c r="AT24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU24" t="n">
         <v>12</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -4847,43 +4914,43 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E25" t="n">
         <v>29</v>
       </c>
       <c r="F25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>0.604</v>
+        <v>0.617</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.5</v>
+        <v>38.7</v>
       </c>
       <c r="J25" t="n">
-        <v>84.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L25" t="n">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="M25" t="n">
         <v>25.3</v>
       </c>
       <c r="N25" t="n">
-        <v>0.369</v>
+        <v>0.371</v>
       </c>
       <c r="O25" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="P25" t="n">
-        <v>24</v>
+        <v>23.9</v>
       </c>
       <c r="Q25" t="n">
         <v>0.76</v>
@@ -4892,16 +4959,16 @@
         <v>11.6</v>
       </c>
       <c r="S25" t="n">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="T25" t="n">
         <v>43.5</v>
       </c>
       <c r="U25" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="V25" t="n">
-        <v>15.1</v>
+        <v>14.9</v>
       </c>
       <c r="W25" t="n">
         <v>8.4</v>
@@ -4916,16 +4983,16 @@
         <v>21.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.7</v>
+        <v>104.9</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AE25" t="n">
         <v>8</v>
@@ -4940,25 +5007,25 @@
         <v>21</v>
       </c>
       <c r="AI25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
         <v>8</v>
       </c>
       <c r="AK25" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AM25" t="n">
         <v>2</v>
       </c>
       <c r="AN25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AO25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AP25" t="n">
         <v>11</v>
@@ -4970,7 +5037,7 @@
         <v>12</v>
       </c>
       <c r="AS25" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT25" t="n">
         <v>13</v>
@@ -4979,7 +5046,7 @@
         <v>30</v>
       </c>
       <c r="AV25" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AW25" t="n">
         <v>8</v>
@@ -5000,7 +5067,7 @@
         <v>6</v>
       </c>
       <c r="BC25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5174,7 @@
         <v>4.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE26" t="n">
         <v>4</v>
@@ -5137,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO26" t="n">
         <v>9</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -5289,16 +5356,16 @@
         <v>-2.2</v>
       </c>
       <c r="AD27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE27" t="n">
         <v>23</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
         <v>12</v>
@@ -5334,7 +5401,7 @@
         <v>10</v>
       </c>
       <c r="AS27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT27" t="n">
         <v>11</v>
@@ -5343,7 +5410,7 @@
         <v>29</v>
       </c>
       <c r="AV27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW27" t="n">
         <v>18</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5483,7 +5550,7 @@
         <v>3</v>
       </c>
       <c r="AH28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -5653,16 +5720,16 @@
         <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE29" t="n">
         <v>11</v>
       </c>
       <c r="AF29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH29" t="n">
         <v>10</v>
@@ -5716,7 +5783,7 @@
         <v>23</v>
       </c>
       <c r="AY29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ29" t="n">
         <v>26</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -5835,19 +5902,19 @@
         <v>-6.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE30" t="n">
         <v>23</v>
       </c>
       <c r="AF30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG30" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH30" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AI30" t="n">
         <v>26</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO30" t="n">
         <v>23</v>
@@ -5907,7 +5974,7 @@
         <v>15</v>
       </c>
       <c r="BB30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC30" t="n">
         <v>28</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6071,7 +6138,7 @@
         <v>8</v>
       </c>
       <c r="AV31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AW31" t="n">
         <v>7</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-4-2013-14</t>
+          <t>2014-02-04</t>
         </is>
       </c>
     </row>
